--- a/templates/library_import_templates.xlsx
+++ b/templates/library_import_templates.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Import" sheetId="1" r:id="R2ef2ad3a62f74b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Book Import" sheetId="2" r:id="Rb4c5e025d0424389"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" r:id="Rae1e59ce76e04194"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Student Import" sheetId="1" r:id="Ra42a05ac0e3c4c18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Book Import" sheetId="2" r:id="Rce7836709355444d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="3" r:id="R0980f5a8ae454727"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,7 @@
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
     <x:numFmt numFmtId="202" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -28,11 +28,16 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFF"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -41,7 +46,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="1F4E78"/>
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF141F52"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -52,7 +62,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="26">
+  <x:cellXfs count="34">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -111,6 +121,24 @@
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -161,9 +189,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -267,14 +295,15 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="35" customHeight="1">
@@ -285,13 +314,13 @@
         <x:v>Name</x:v>
       </x:c>
       <x:c r="C1" s="16" t="str">
-        <x:v>Group</x:v>
+        <x:v>Section</x:v>
       </x:c>
       <x:c r="D1" s="16" t="str">
-        <x:v>Department</x:v>
+        <x:v>Department / Strand</x:v>
       </x:c>
       <x:c r="E1" s="16" t="str">
-        <x:v>Yr Lvl</x:v>
+        <x:v>Grade Level</x:v>
       </x:c>
       <x:c r="F1" s="16" t="str">
         <x:v>Contact Number</x:v>
@@ -301,6 +330,9 @@
       </x:c>
       <x:c r="H1" s="16" t="str">
         <x:v>Email</x:v>
+      </x:c>
+      <x:c r="I1" s="12" t="str">
+        <x:v>Password</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -313,9 +345,7 @@
       <x:c r="C2" s="14" t="str">
         <x:v>9-A</x:v>
       </x:c>
-      <x:c r="D2" s="14" t="str">
-        <x:v>Junior High School</x:v>
-      </x:c>
+      <x:c r="D2" s="14" t="str"/>
       <x:c r="E2" s="14" t="str">
         <x:v>Grade 9</x:v>
       </x:c>
@@ -328,9 +358,38 @@
       <x:c r="H2" s="14" t="str">
         <x:v>juan.delacruz@example.com</x:v>
       </x:c>
+      <x:c r="I2" s="12" t="str">
+        <x:v>JasHs!2026A</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="G3" s="19"/>
+      <x:c r="A3" t="str">
+        <x:v>S-0002</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>Maria Santos</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>11-A</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>STEM</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>Grade 11</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>09987654321</x:v>
+      </x:c>
+      <x:c r="G3" s="19" t="str">
+        <x:v>2026-12-31</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>maria.santos@example.com</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="str">
+        <x:v>Library#2026B</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="G4" s="19"/>
@@ -1824,6 +1883,14 @@
       <x:c r="G500" s="19"/>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="E2:E100">
+      <x:formula1>"Grade 7,Grade 8,Grade 9,Grade 10,Grade 11,Grade 12"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D2:D100">
+      <x:formula1>"STEM,ABM,HUMSS,GAS,TVL,Arts and Design,Sports"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -1833,46 +1900,70 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="35" customHeight="1">
-      <x:c r="A1" s="16" t="str">
+      <x:c r="A1" s="27" t="str">
         <x:v>Title</x:v>
       </x:c>
-      <x:c r="B1" s="16" t="str">
+      <x:c r="B1" s="27" t="str">
         <x:v>Author</x:v>
       </x:c>
-      <x:c r="C1" s="16" t="str">
+      <x:c r="C1" s="27" t="str">
         <x:v>Co-Authors</x:v>
       </x:c>
-      <x:c r="D1" s="16" t="str">
+      <x:c r="D1" s="27" t="str">
         <x:v>Place of Publication</x:v>
       </x:c>
-      <x:c r="E1" s="16" t="str">
+      <x:c r="E1" s="27" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="F1" s="16" t="str">
-        <x:v>Call Number of Book</x:v>
-      </x:c>
-      <x:c r="G1" s="16" t="str">
-        <x:v>Accession Number / Bar Code Number</x:v>
-      </x:c>
-      <x:c r="H1" s="16" t="str">
+      <x:c r="F1" s="27" t="str">
+        <x:v>Book Number</x:v>
+      </x:c>
+      <x:c r="G1" s="27" t="str">
+        <x:v>Book Pages</x:v>
+      </x:c>
+      <x:c r="H1" s="27" t="str">
+        <x:v>Source of Funds</x:v>
+      </x:c>
+      <x:c r="I1" s="27" t="str">
+        <x:v>Cost Price</x:v>
+      </x:c>
+      <x:c r="J1" s="27" t="str">
+        <x:v>Publisher</x:v>
+      </x:c>
+      <x:c r="K1" s="32" t="str">
+        <x:v>Edition</x:v>
+      </x:c>
+      <x:c r="L1" s="32" t="str">
+        <x:v>Volumes</x:v>
+      </x:c>
+      <x:c r="M1" s="32" t="str">
+        <x:v>Class</x:v>
+      </x:c>
+      <x:c r="N1" s="32" t="str">
         <x:v>Type of Material</x:v>
       </x:c>
-      <x:c r="I1" s="16" t="str">
+      <x:c r="O1" s="32" t="str">
         <x:v>Number of Copies</x:v>
       </x:c>
-      <x:c r="J1" s="16" t="str">
+      <x:c r="P1" s="32" t="str">
         <x:v>Location / Collection</x:v>
       </x:c>
     </x:row>
@@ -1883,7 +1974,7 @@
       <x:c r="B2" s="14" t="str">
         <x:v>Jose Rizal</x:v>
       </x:c>
-      <x:c r="C2" s="14" t="str"/>
+      <x:c r="C2" s="14"/>
       <x:c r="D2" s="14" t="str">
         <x:v>Manila</x:v>
       </x:c>
@@ -1891,18 +1982,24 @@
         <x:v>1887-01-01</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>FIL 899.211 RIZ n</x:v>
-      </x:c>
-      <x:c r="G2" s="14" t="str">
-        <x:v>ACC-0001</x:v>
-      </x:c>
-      <x:c r="H2" s="14" t="str">
+        <x:v>BOOK-0001</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H2" s="14"/>
+      <x:c r="I2" s="22"/>
+      <x:c r="J2" s="14"/>
+      <x:c r="K2" s="12"/>
+      <x:c r="L2" s="12"/>
+      <x:c r="M2" s="12"/>
+      <x:c r="N2" s="12" t="str">
         <x:v>Book</x:v>
       </x:c>
-      <x:c r="I2" s="22" t="n">
+      <x:c r="O2" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J2" s="14" t="str">
+      <x:c r="P2" s="12" t="str">
         <x:v>Filipiniana</x:v>
       </x:c>
     </x:row>
@@ -1913,7 +2010,7 @@
       <x:c r="B3" s="14" t="str">
         <x:v>Jose Rizal</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str"/>
+      <x:c r="C3" s="14"/>
       <x:c r="D3" s="14" t="str">
         <x:v>Ghent</x:v>
       </x:c>
@@ -1921,18 +2018,24 @@
         <x:v>1891-01-01</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
-        <x:v>FIL 899.211 RIZ e</x:v>
-      </x:c>
-      <x:c r="G3" s="14" t="str">
-        <x:v>ACC-0002</x:v>
-      </x:c>
-      <x:c r="H3" s="14" t="str">
+        <x:v>BOOK-0002</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H3" s="14"/>
+      <x:c r="I3" s="22"/>
+      <x:c r="J3" s="14"/>
+      <x:c r="K3" s="12"/>
+      <x:c r="L3" s="12"/>
+      <x:c r="M3" s="12"/>
+      <x:c r="N3" s="12" t="str">
         <x:v>Book</x:v>
       </x:c>
-      <x:c r="I3" s="22" t="n">
+      <x:c r="O3" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J3" s="14" t="str">
+      <x:c r="P3" s="12" t="str">
         <x:v>Filipiniana</x:v>
       </x:c>
     </x:row>
@@ -1943,7 +2046,7 @@
       <x:c r="B4" s="14" t="str">
         <x:v>Francisco Balagtas</x:v>
       </x:c>
-      <x:c r="C4" s="14" t="str"/>
+      <x:c r="C4" s="14"/>
       <x:c r="D4" s="14" t="str">
         <x:v>Manila</x:v>
       </x:c>
@@ -1951,18 +2054,24 @@
         <x:v>1838-01-01</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
-        <x:v>FIL 899.211 BAL f</x:v>
-      </x:c>
-      <x:c r="G4" s="14" t="str">
-        <x:v>ACC-0003</x:v>
-      </x:c>
-      <x:c r="H4" s="14" t="str">
+        <x:v>BOOK-0003</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H4" s="14"/>
+      <x:c r="I4" s="22"/>
+      <x:c r="J4" s="14"/>
+      <x:c r="K4" s="12"/>
+      <x:c r="L4" s="12"/>
+      <x:c r="M4" s="12"/>
+      <x:c r="N4" s="12" t="str">
         <x:v>Book</x:v>
       </x:c>
-      <x:c r="I4" s="22" t="n">
+      <x:c r="O4" s="12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J4" s="14" t="str">
+      <x:c r="P4" s="12" t="str">
         <x:v>Filipiniana</x:v>
       </x:c>
     </x:row>
@@ -3959,55 +4068,95 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="110" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="95" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="4" t="str">
+      <x:c r="A1" s="30" t="str">
         <x:v>Import Template Notes</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="33" t="str">
         <x:v>Book Import</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="12" t="str">
-        <x:v>Required book fields: Title, Author, Place of Publication, Date, Call Number of Book, Accession Number / Bar Code Number, Type of Material, Number of Copies, Location / Collection.</x:v>
+        <x:v>Required book fields: Title, Author, Place of Publication, Date, Book Number, Book Pages, Type of Material, Number of Copies, Location / Collection.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="12" t="str">
-        <x:v>Co-Authors can be blank or separated by semicolon, example: Author One; Author Two; Author Three.</x:v>
+        <x:v>Optional book fields: Co-Authors, Source of Funds, Cost Price, Publisher, Edition, Volumes, and Class.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="12" t="str">
-        <x:v>Date format should be YYYY-MM-DD.</x:v>
+        <x:v>Book Number must be unique for each book record.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="12" t="str">
-        <x:v>Number of Copies should be a whole number, e.g. 1, 2, 3.</x:v>
+        <x:v>Book Pages should be a whole number greater than 0.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="12" t="str"/>
+      <x:c r="A7" s="12" t="str">
+        <x:v>Co-Authors can be blank or separated by semicolon, example: Author One; Author Two; Author Three.</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="12" t="str">
-        <x:v>Student Import</x:v>
+        <x:v>Date format should be YYYY-MM-DD.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="str">
-        <x:v>Required student fields: Student No and Name.</x:v>
+        <x:v>Number of Copies should be a whole number, e.g. 1, 2, 3.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="12" t="str">
-        <x:v>Validity of Library Access Card should use YYYY-MM-DD.</x:v>
+      <x:c r="A10" s="12"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="33" t="str">
+        <x:v>Student Import</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="12" t="str">
+        <x:v>Required student fields: Student No, Name, Section, Grade Level, Email, and Password.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="12" t="str">
+        <x:v>Grade Level must be Grade 7, Grade 8, Grade 9, Grade 10, Grade 11, or Grade 12.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="12" t="str">
+        <x:v>Department / Strand is required only for Grade 11 and Grade 12. Leave it blank for Grade 7 to Grade 10.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="12" t="str">
+        <x:v>Senior High School strand choices: STEM, ABM, HUMSS, GAS, TVL, Arts and Design, Sports.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="12" t="str">
+        <x:v>Student passwords must be at least 10 characters and include uppercase, lowercase, a number, and a special character.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="12" t="str">
+        <x:v>Student login uses the password plus a 6-digit email verification code sent to the registered email address.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="12" t="str">
+        <x:v>Existing database passwords are not changed by this security update.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
